--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/WYOMING_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/WYOMING_2016.xlsx
@@ -1608,7 +1608,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C70">
@@ -5431,7 +5431,7 @@
         <v>88</v>
       </c>
       <c r="D282">
-        <v>0.09988649262202043</v>
+        <v>0.09988649262202044</v>
       </c>
     </row>
     <row r="283">
